--- a/02 Master/S1 TU Dresden/01 Climatology and Hydrology/Hydrology/Exercise/exercise03_data.xlsx
+++ b/02 Master/S1 TU Dresden/01 Climatology and Hydrology/Hydrology/Exercise/exercise03_data.xlsx
@@ -1,32 +1,109 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Obsidian Vault\Apuntes\02 Master\S1 TU Dresden\01 Climatology and Hydrology\Hydrology\Exercise\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB7AA8C-8C6C-4270-A51E-C32C675E00E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>1 hr</t>
+  </si>
+  <si>
+    <t>3 hrs</t>
+  </si>
+  <si>
+    <t>6 hrs</t>
+  </si>
+  <si>
+    <t>12 hrs</t>
+  </si>
+  <si>
+    <t>24 hrs</t>
+  </si>
+  <si>
+    <t>Empirical Mean</t>
+  </si>
+  <si>
+    <t>Std</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t> Euler-Mascheroni </t>
+  </si>
+  <si>
+    <t>RP</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +114,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +122,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +171,1255 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>DDF</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RP: 2y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$17:$K$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$L$17:$L$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.930027872541011</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.867434708022397</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.328033786506744</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45.626339124795912</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>59.101273187187743</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BCF7-4824-A2CC-7CD6EAAE3DE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RP: 10y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$17:$K$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$M$17:$M$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.364575231177795</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.202879696095721</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42.687927060923094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>59.54817243847306</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85.765305756067249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BCF7-4824-A2CC-7CD6EAAE3DE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>RP: 50y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$17:$K$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$N$17:$N$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28.759125762545104</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42.263943316802845</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.770424444591285</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71.753415417142733</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>109.14160893121121</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BCF7-4824-A2CC-7CD6EAAE3DE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>RP: 100y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$17:$K$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$O$17:$O$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31.885211349704598</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46.094556180812873</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55.610098545952646</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>76.913246836449275</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>119.02406549525823</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BCF7-4824-A2CC-7CD6EAAE3DE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1695837919"/>
+        <c:axId val="1695832639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1695837919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="24"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1695832639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1695832639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1695837919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7092091-ECED-A5F6-C4B7-50F0C3EFF294}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +1684,1008 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C2:P38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="2">
+        <v>1988</v>
+      </c>
+      <c r="D4" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="F4" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="G4" s="2">
+        <v>48.8</v>
+      </c>
+      <c r="H4" s="2">
+        <v>62.2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <f>$I$38+($I$37*(-LN(-LN((K4-1)/K4))))</f>
+        <v>13.130934176480281</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="2">
+        <v>1989</v>
+      </c>
+      <c r="D5" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E5" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2">
+        <v>56.4</v>
+      </c>
+      <c r="H5" s="2">
+        <v>85</v>
+      </c>
+      <c r="K5" s="5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L7" si="0">$I$38+($I$37*(-LN(-LN((K5-1)/K5))))</f>
+        <v>21.79581731544576</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="2">
+        <v>1990</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2">
+        <v>25.7</v>
+      </c>
+      <c r="G6" s="2">
+        <v>38.1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>45</v>
+      </c>
+      <c r="K6" s="5">
+        <v>50</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>29.392302757413614</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="2">
+        <v>1991</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>21.8</v>
+      </c>
+      <c r="G7" s="2">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2">
+        <v>36.6</v>
+      </c>
+      <c r="K7" s="5">
+        <v>100</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>32.603757402624026</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="2">
+        <v>1992</v>
+      </c>
+      <c r="D8" s="2">
+        <v>12</v>
+      </c>
+      <c r="E8" s="2">
+        <v>21.7</v>
+      </c>
+      <c r="F8" s="2">
+        <v>31.9</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46.8</v>
+      </c>
+      <c r="H8" s="2">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="2">
+        <v>1993</v>
+      </c>
+      <c r="D9" s="2">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2">
+        <v>22.3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>32.4</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46.9</v>
+      </c>
+      <c r="H9" s="2">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="2">
+        <v>1994</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2">
+        <v>25.7</v>
+      </c>
+      <c r="G10" s="2">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="H10" s="2">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="2">
+        <v>1995</v>
+      </c>
+      <c r="D11" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="F11" s="2">
+        <v>33</v>
+      </c>
+      <c r="G11" s="2">
+        <v>48.2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>61.6</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>6</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="2">
+        <v>1996</v>
+      </c>
+      <c r="D12" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E12" s="2">
+        <v>29.4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="G12" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="H12" s="2">
+        <v>85.3</v>
+      </c>
+      <c r="K12" s="5">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <f>$D$38+($D$37*(-LN(-LN(($K$12-1)/$K$12))))</f>
+        <v>12.930027872541011</v>
+      </c>
+      <c r="M12">
+        <f>$E$38+($E$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>22.867434708022397</v>
+      </c>
+      <c r="N12">
+        <f>$F$38+($F$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>32.328033786506744</v>
+      </c>
+      <c r="O12">
+        <f>$G$38+($G$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>45.626339124795912</v>
+      </c>
+      <c r="P12">
+        <f>$H$38+($H$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>59.101273187187743</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="2">
+        <v>1997</v>
+      </c>
+      <c r="D13" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="E13" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>37.6</v>
+      </c>
+      <c r="G13" s="2">
+        <v>50.3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>67.3</v>
+      </c>
+      <c r="K13" s="5">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <f>$D$38+($D$37*(-LN(-LN(($K$13-1)/$K$13))))</f>
+        <v>21.364575231177795</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:O15" si="1">$E$38+($E$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>33.202879696095721</v>
+      </c>
+      <c r="N13">
+        <f t="shared" ref="N13:N15" si="2">$F$38+($F$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>42.687927060923094</v>
+      </c>
+      <c r="O13">
+        <f t="shared" ref="O13:P15" si="3">$G$38+($G$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>59.54817243847306</v>
+      </c>
+      <c r="P13">
+        <f t="shared" ref="P13:P15" si="4">$H$38+($H$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>85.765305756067249</v>
+      </c>
+    </row>
+    <row r="14" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="2">
+        <v>1998</v>
+      </c>
+      <c r="D14" s="2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E14" s="2">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="F14" s="2">
+        <v>41.7</v>
+      </c>
+      <c r="G14" s="2">
+        <v>58</v>
+      </c>
+      <c r="H14" s="2">
+        <v>92.6</v>
+      </c>
+      <c r="K14" s="5">
+        <v>50</v>
+      </c>
+      <c r="L14">
+        <f>$D$38+($D$37*(-LN(-LN(($K$14-1)/$K$14))))</f>
+        <v>28.759125762545104</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="1"/>
+        <v>42.263943316802845</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="2"/>
+        <v>51.770424444591285</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="3"/>
+        <v>71.753415417142733</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="4"/>
+        <v>109.14160893121121</v>
+      </c>
+    </row>
+    <row r="15" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="2">
+        <v>1999</v>
+      </c>
+      <c r="D15" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="G15" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>68.5</v>
+      </c>
+      <c r="K15" s="5">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <f>$D$38+($D$37*(-LN(-LN(($K$15-1)/$K$15))))</f>
+        <v>31.885211349704598</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>46.094556180812873</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>55.610098545952646</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="3"/>
+        <v>76.913246836449275</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="4"/>
+        <v>119.02406549525823</v>
+      </c>
+    </row>
+    <row r="16" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="2">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="E16" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="G16" s="2">
+        <v>41.1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D17" s="2">
+        <v>35.6</v>
+      </c>
+      <c r="E17" s="2">
+        <v>44.4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="G17" s="2">
+        <v>70.3</v>
+      </c>
+      <c r="H17" s="2">
+        <v>110</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="2">
+        <v>2002</v>
+      </c>
+      <c r="D18" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="E18" s="2">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2">
+        <v>36</v>
+      </c>
+      <c r="G18" s="2">
+        <v>49.6</v>
+      </c>
+      <c r="H18" s="2">
+        <v>63.1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <f>$D$38+($D$37*(-LN(-LN(($K$12-1)/$K$12))))</f>
+        <v>12.930027872541011</v>
+      </c>
+      <c r="M18">
+        <f>$D$38+($D$37*(-LN(-LN(($K$13-1)/$K$13))))</f>
+        <v>21.364575231177795</v>
+      </c>
+      <c r="N18">
+        <f>$D$38+($D$37*(-LN(-LN(($K$14-1)/$K$14))))</f>
+        <v>28.759125762545104</v>
+      </c>
+      <c r="O18">
+        <f>$D$38+($D$37*(-LN(-LN(($K$15-1)/$K$15))))</f>
+        <v>31.885211349704598</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D19" s="2">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="F19" s="2">
+        <v>28.3</v>
+      </c>
+      <c r="G19" s="2">
+        <v>40</v>
+      </c>
+      <c r="H19" s="2">
+        <v>51.9</v>
+      </c>
+      <c r="K19" s="1">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <f>$E$38+($E$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>22.867434708022397</v>
+      </c>
+      <c r="M19">
+        <f>$E$38+($E$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>33.202879696095721</v>
+      </c>
+      <c r="N19">
+        <f>$E$38+($E$37*(-LN(-LN(($K14-1)/$K14))))</f>
+        <v>42.263943316802845</v>
+      </c>
+      <c r="O19">
+        <f>$E$38+($E$37*(-LN(-LN(($K15-1)/$K15))))</f>
+        <v>46.094556180812873</v>
+      </c>
+    </row>
+    <row r="20" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="2">
+        <v>2004</v>
+      </c>
+      <c r="D20" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="E20" s="2">
+        <v>18.2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="G20" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="H20" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="K20" s="1">
+        <v>6</v>
+      </c>
+      <c r="L20">
+        <f>$F$38+($F$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>32.328033786506744</v>
+      </c>
+      <c r="M20">
+        <f>$F$38+($F$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>42.687927060923094</v>
+      </c>
+      <c r="N20">
+        <f>$F$38+($F$37*(-LN(-LN(($K14-1)/$K14))))</f>
+        <v>51.770424444591285</v>
+      </c>
+      <c r="O20">
+        <f>$F$38+($F$37*(-LN(-LN(($K15-1)/$K15))))</f>
+        <v>55.610098545952646</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="2">
+        <v>2005</v>
+      </c>
+      <c r="D21" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="E21" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>31.7</v>
+      </c>
+      <c r="G21" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="H21" s="2">
+        <v>56.4</v>
+      </c>
+      <c r="K21" s="1">
+        <v>12</v>
+      </c>
+      <c r="L21">
+        <f>$G$38+($G$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>45.626339124795912</v>
+      </c>
+      <c r="M21">
+        <f>$G$38+($G$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>59.54817243847306</v>
+      </c>
+      <c r="N21">
+        <f>$G$38+($G$37*(-LN(-LN(($K14-1)/$K14))))</f>
+        <v>71.753415417142733</v>
+      </c>
+      <c r="O21">
+        <f>$G$38+($G$37*(-LN(-LN(($K15-1)/$K15))))</f>
+        <v>76.913246836449275</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="2">
+        <v>2006</v>
+      </c>
+      <c r="D22" s="2">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="F22" s="2">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="G22" s="2">
+        <v>53.7</v>
+      </c>
+      <c r="H22" s="2">
+        <v>69</v>
+      </c>
+      <c r="K22" s="1">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <f>$H$38+($H$37*(-LN(-LN(($K12-1)/$K12))))</f>
+        <v>59.101273187187743</v>
+      </c>
+      <c r="M22">
+        <f>$H$38+($H$37*(-LN(-LN(($K13-1)/$K13))))</f>
+        <v>85.765305756067249</v>
+      </c>
+      <c r="N22">
+        <f>$H$38+($H$37*(-LN(-LN(($K14-1)/$K14))))</f>
+        <v>109.14160893121121</v>
+      </c>
+      <c r="O22">
+        <f>$H$38+($H$37*(-LN(-LN(($K15-1)/$K15))))</f>
+        <v>119.02406549525823</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="2">
+        <v>2007</v>
+      </c>
+      <c r="D23" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="F23" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G23" s="2">
+        <v>48</v>
+      </c>
+      <c r="H23" s="2">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="2">
+        <v>2008</v>
+      </c>
+      <c r="D24" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="E24" s="2">
+        <v>25.1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="G24" s="2">
+        <v>50</v>
+      </c>
+      <c r="H24" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="2">
+        <v>2009</v>
+      </c>
+      <c r="D25" s="2">
+        <v>16.7</v>
+      </c>
+      <c r="E25" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="F25" s="2">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="G25" s="2">
+        <v>56.4</v>
+      </c>
+      <c r="H25" s="2">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="2">
+        <v>2010</v>
+      </c>
+      <c r="D26" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E26" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="F26" s="2">
+        <v>26.9</v>
+      </c>
+      <c r="G26" s="2">
+        <v>39.9</v>
+      </c>
+      <c r="H26" s="2">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="2">
+        <v>2011</v>
+      </c>
+      <c r="D27" s="2">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2">
+        <v>25</v>
+      </c>
+      <c r="G27" s="2">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="H27" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C28" s="2">
+        <v>2012</v>
+      </c>
+      <c r="D28" s="2">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>41.9</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45.7</v>
+      </c>
+      <c r="G28" s="2">
+        <v>62.3</v>
+      </c>
+      <c r="H28" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C29" s="2">
+        <v>2013</v>
+      </c>
+      <c r="D29" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="G29" s="2">
+        <v>48.7</v>
+      </c>
+      <c r="H29" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C30" s="2">
+        <v>2014</v>
+      </c>
+      <c r="D30" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="E30" s="2">
+        <v>22.7</v>
+      </c>
+      <c r="F30" s="2">
+        <v>32.4</v>
+      </c>
+      <c r="G30" s="2">
+        <v>47.1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D31" s="2">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2">
+        <v>20.3</v>
+      </c>
+      <c r="G31" s="2">
+        <v>27.4</v>
+      </c>
+      <c r="H31" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D32" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="E32" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="G32" s="2">
+        <v>55.3</v>
+      </c>
+      <c r="H32" s="2">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D33" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="E33" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F33" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="G33" s="2">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="H33" s="2">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K34">
+        <f>0.5772</f>
+        <v>0.57720000000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <f>AVERAGE(D4:D33)</f>
+        <v>13.873333333333331</v>
+      </c>
+      <c r="E35">
+        <f t="shared" ref="E35:H35" si="5">AVERAGE(E4:E33)</f>
+        <v>24.023333333333326</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="5"/>
+        <v>33.486666666666665</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="5"/>
+        <v>47.18333333333333</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="5"/>
+        <v>62.083333333333336</v>
+      </c>
+      <c r="I35">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <f>_xlfn.STDEV.S(D4:D33)</f>
+        <v>5.7423372229092617</v>
+      </c>
+      <c r="E36">
+        <f t="shared" ref="E36:H36" si="6">_xlfn.STDEV.S(E4:E33)</f>
+        <v>7.0364902758619001</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="6"/>
+        <v>7.0531349514721642</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="6"/>
+        <v>9.4781448546146105</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="6"/>
+        <v>18.153181222742976</v>
+      </c>
+      <c r="I36">
+        <f>SQRT(34.8)</f>
+        <v>5.8991524815010496</v>
+      </c>
+    </row>
+    <row r="37" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <f>SQRT(6)*(D36/PI())</f>
+        <v>4.477281964307422</v>
+      </c>
+      <c r="E37">
+        <f t="shared" ref="E37:I37" si="7">SQRT(6)*(E36/PI())</f>
+        <v>5.4863289600013898</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="7"/>
+        <v>5.4993067603322849</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="7"/>
+        <v>7.3900792247724372</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="7"/>
+        <v>14.153977331587932</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="7"/>
+        <v>4.5995503198160703</v>
+      </c>
+    </row>
+    <row r="38" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38">
+        <f>D35-($K$34*D37)</f>
+        <v>11.289046183535087</v>
+      </c>
+      <c r="E38">
+        <f t="shared" ref="E38:I38" si="8">E35-($K$34*E37)</f>
+        <v>20.856624257620524</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="8"/>
+        <v>30.31246680460287</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="8"/>
+        <v>42.917779604794681</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="8"/>
+        <v>53.913657617540778</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="8"/>
+        <v>11.445139555402164</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>